--- a/Otros_Actores.xlsx
+++ b/Otros_Actores.xlsx
@@ -1,52 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Propietario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios GitHub\Capturaradio\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D8854D-5520-446C-B90A-816C77A91CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Legisladores locales" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
-  <si>
-    <t>Diputado</t>
-  </si>
-  <si>
-    <t>Grupo legislativo</t>
-  </si>
-  <si>
-    <t>José María Alejandro Pérez Ramírez</t>
-  </si>
-  <si>
-    <t>GLPanalh</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="262">
   <si>
     <t>Alhely Medina Hernández</t>
   </si>
   <si>
-    <t>GLMorena</t>
-  </si>
-  <si>
-    <t>Julián Nochebuena Hernández</t>
-  </si>
-  <si>
     <t>Paloma Barragán Santos</t>
   </si>
   <si>
@@ -77,9 +71,6 @@
     <t>Andrés Velázquez Vázquez</t>
   </si>
   <si>
-    <t>Junta de Gobierno</t>
-  </si>
-  <si>
     <t>José Luis Rodríguez Higareda</t>
   </si>
   <si>
@@ -89,70 +80,754 @@
     <t>Juan Pablo Escalante Urban</t>
   </si>
   <si>
-    <t>Hilda Miranda Miranda</t>
-  </si>
-  <si>
-    <t>Mónica Leanett Reyes Martínez</t>
-  </si>
-  <si>
-    <t>Claudia Lilia Luna Islas</t>
-  </si>
-  <si>
-    <t>GLPAN</t>
-  </si>
-  <si>
-    <t>Marco Antonio Mendoza Bustamante</t>
-  </si>
-  <si>
-    <t>GLPRI</t>
-  </si>
-  <si>
     <t>Avelino Tovar Iglesias</t>
   </si>
   <si>
-    <t>GLPVEM</t>
-  </si>
-  <si>
-    <t>Francisco Javier Téllez Sánchez</t>
-  </si>
-  <si>
-    <t>GLPT</t>
-  </si>
-  <si>
     <t>Karla Perales Arrieta</t>
   </si>
   <si>
-    <t>GLMC</t>
-  </si>
-  <si>
     <t>Jorge Argüelles Salazar</t>
   </si>
   <si>
-    <t>Juana Olivia Alarcón Rivera</t>
-  </si>
-  <si>
-    <t>Orquídea Larragoiti Osorio</t>
-  </si>
-  <si>
     <t>María Guadalupe Cruz Montaño</t>
   </si>
   <si>
-    <t>Carlos Alejandro Alcántara Carbajal</t>
-  </si>
-  <si>
     <t>Leonel Perusquia Muedano</t>
   </si>
   <si>
-    <t>GLPRD</t>
-  </si>
-  <si>
-    <t>Johana Montcerrat Hernández Pérez</t>
+    <t>Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Edda Vite</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>María Esther Ramírez Vargas</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Alejandro Sánchez García</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>Carlos Henkel</t>
+  </si>
+  <si>
+    <t>Mónica Mixtega</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Lyzbeth Robles</t>
+  </si>
+  <si>
+    <t>Francisco Fernández Hasbun</t>
+  </si>
+  <si>
+    <t>Onésimo Serrano Rivera</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Edgar Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>Alejandro Velázquez Mendoza</t>
+  </si>
+  <si>
+    <t>Juan Evel Chávez</t>
+  </si>
+  <si>
+    <t>Mariela Valero Mota</t>
+  </si>
+  <si>
+    <t>Luisa Yuriley Gonzaga Ramírez</t>
+  </si>
+  <si>
+    <t>Prisco Manuel Gutiérrez</t>
+  </si>
+  <si>
+    <t>Francisco Patiño</t>
+  </si>
+  <si>
+    <t>Isabel Sepúlveda Montaño</t>
+  </si>
+  <si>
+    <t>Erika Ortigoza</t>
+  </si>
+  <si>
+    <t>Alejandro Franco Segura</t>
+  </si>
+  <si>
+    <t>Ricardo Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>Jorge Acosta Benítez</t>
+  </si>
+  <si>
+    <t>Carlos Arturo Sanchez Lugo</t>
+  </si>
+  <si>
+    <t>Katya Hernández Pérez</t>
+  </si>
+  <si>
+    <t>Abel Cerón San Nicolás</t>
+  </si>
+  <si>
+    <t>Oscar Pérez Rojas</t>
+  </si>
+  <si>
+    <t>Cristian Miguel Catalán</t>
+  </si>
+  <si>
+    <t>Edmundo Pineda</t>
+  </si>
+  <si>
+    <t>Marco Antonio Aranzábal</t>
+  </si>
+  <si>
+    <t>Román Bernal Díaz</t>
+  </si>
+  <si>
+    <t>Andrés Torres</t>
+  </si>
+  <si>
+    <t>Carlos Barra Moulain</t>
+  </si>
+  <si>
+    <t>Ricardo Olvera Molina</t>
+  </si>
+  <si>
+    <t>Bertha Miranda</t>
+  </si>
+  <si>
+    <t>Celia Ramírez Godínez</t>
+  </si>
+  <si>
+    <t>Lucero Cerón Ordoñez</t>
+  </si>
+  <si>
+    <t>Brenda Flores Alarcón</t>
+  </si>
+  <si>
+    <t>Daniel Fragoso</t>
+  </si>
+  <si>
+    <t>Edgar Manuel Castillo Flores</t>
+  </si>
+  <si>
+    <t>Edmundo Ramírez Martínez</t>
+  </si>
+  <si>
+    <t>Iván Enrique Ramírez Alcázar</t>
+  </si>
+  <si>
+    <t>Jorge Armando Cruz León</t>
+  </si>
+  <si>
+    <t>Juan Antonio Ter Veen Becerra</t>
+  </si>
+  <si>
+    <t>Leoncio Marañón Priego</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite</t>
+  </si>
+  <si>
+    <t>Norma Ivonne Luna Campos</t>
+  </si>
+  <si>
+    <t>Pablo Vargas</t>
+  </si>
+  <si>
+    <t>Xóchitl Beatriz García Curiel</t>
+  </si>
+  <si>
+    <t>Humberto Cabrera</t>
+  </si>
+  <si>
+    <t>José Antonio Pérez Sánchez</t>
+  </si>
+  <si>
+    <t>Jerusalem Kuri del Campo</t>
+  </si>
+  <si>
+    <t>Penélope Apodaca Sinsel</t>
+  </si>
+  <si>
+    <t>Juan Carlos Chávez González</t>
+  </si>
+  <si>
+    <t>Erika Toledo parra</t>
+  </si>
+  <si>
+    <t>León Peña Barquera</t>
+  </si>
+  <si>
+    <t>Roberto Carrillo Partido</t>
+  </si>
+  <si>
+    <t>Carlos Martín Pérez Quijano</t>
+  </si>
+  <si>
+    <t>Cinthya Yarely Meza Cortes</t>
+  </si>
+  <si>
+    <t>Abril Martínez Portillo</t>
+  </si>
+  <si>
+    <t>Alberto Basilio González</t>
+  </si>
+  <si>
+    <t>Alejandro Flores Hernández</t>
+  </si>
+  <si>
+    <t>Amado Pérez Hernández</t>
+  </si>
+  <si>
+    <t>Ana Elsa Castillo Cea</t>
+  </si>
+  <si>
+    <t>Ana María Rivera Contreras</t>
+  </si>
+  <si>
+    <t>Anna Laura Ibarra García</t>
+  </si>
+  <si>
+    <t>Armando Zúñiga Gutiérrez</t>
+  </si>
+  <si>
+    <t>Belem Oliver González</t>
+  </si>
+  <si>
+    <t>Carlos César Pérez Escamilla</t>
+  </si>
+  <si>
+    <t>Carlos Montaño Rodríguez</t>
+  </si>
+  <si>
+    <t>Christian Buendía</t>
+  </si>
+  <si>
+    <t>Claudia Arisbee Sandoval</t>
+  </si>
+  <si>
+    <t>Claudia Sandoval Ramírez</t>
+  </si>
+  <si>
+    <t>Corina Jiménez Melo</t>
+  </si>
+  <si>
+    <t>Cristhian Martínez Resendiz</t>
+  </si>
+  <si>
+    <t>Cynthia Arrellano Martínez</t>
+  </si>
+  <si>
+    <t>Danay Ángeles Hernández</t>
+  </si>
+  <si>
+    <t>David Medina Hernández</t>
+  </si>
+  <si>
+    <t>Diana López Rangel</t>
+  </si>
+  <si>
+    <t>Diana Moreno Rea</t>
+  </si>
+  <si>
+    <t>Edmundo Méndez Tejeda</t>
+  </si>
+  <si>
+    <t>Eduardo Medécigo</t>
+  </si>
+  <si>
+    <t>Eligio Figueroa Chávez</t>
+  </si>
+  <si>
+    <t>Emmanuel Hernández Pascual</t>
+  </si>
+  <si>
+    <t>Enrique Estrada Corres</t>
+  </si>
+  <si>
+    <t>Erik José Ramírez Montaño</t>
+  </si>
+  <si>
+    <t>Erika Hernández Ramírez</t>
+  </si>
+  <si>
+    <t>Febronio Rodríguez Villegas</t>
+  </si>
+  <si>
+    <t>Félix Ávila Castelán</t>
+  </si>
+  <si>
+    <t>Fernando Baltazar Monzalvo</t>
+  </si>
+  <si>
+    <t>Francisca Lara Velázquez</t>
+  </si>
+  <si>
+    <t>Francisco Martínez Enríquez</t>
+  </si>
+  <si>
+    <t>Gabino Hernández Vite</t>
+  </si>
+  <si>
+    <t>Gabriela Escamilla López</t>
+  </si>
+  <si>
+    <t>Germán Hernández Pérez</t>
+  </si>
+  <si>
+    <t>Gretchen Atilano Moreno</t>
+  </si>
+  <si>
+    <t>Guillermo Amador Lara</t>
+  </si>
+  <si>
+    <t>Hermilio Trejo Rangel</t>
+  </si>
+  <si>
+    <t>Ibsan Israel Villeda Villeda</t>
+  </si>
+  <si>
+    <t>Imelda Cuéllar Cano</t>
+  </si>
+  <si>
+    <t>Isabel Ramírez Mercado</t>
+  </si>
+  <si>
+    <t>Jensen Benony Oropeza</t>
+  </si>
+  <si>
+    <t>Jorge Alberto Hernández Cortés</t>
+  </si>
+  <si>
+    <t>Jorge Hernández Araus</t>
+  </si>
+  <si>
+    <t>Jorge Reyes</t>
+  </si>
+  <si>
+    <t>José Alfredo San Román</t>
+  </si>
+  <si>
+    <t>José Christian Buendía Andrade</t>
+  </si>
+  <si>
+    <t>Juan Antonio Franco Ortiz</t>
+  </si>
+  <si>
+    <t>Juan de Dios Nochebuena</t>
+  </si>
+  <si>
+    <t>Julio Agustín Cruz Tovar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karla Hernández Cerroblanco </t>
+  </si>
+  <si>
+    <t>Kendra Martínez Sánchez</t>
+  </si>
+  <si>
+    <t>Leticia Chapa</t>
+  </si>
+  <si>
+    <t>Leticia Reyes Reyes</t>
+  </si>
+  <si>
+    <t>Lorena Estrada Flores</t>
+  </si>
+  <si>
+    <t>Lorena García Cázares</t>
+  </si>
+  <si>
+    <t>Luis Enrique Tapia Zapata</t>
+  </si>
+  <si>
+    <t>Luis Felipe Lugo Salinas</t>
+  </si>
+  <si>
+    <t>María Díaz Bustos</t>
+  </si>
+  <si>
+    <t>Maricela Hernández Lugo</t>
+  </si>
+  <si>
+    <t>Marina Ramírez Sánchez</t>
+  </si>
+  <si>
+    <t>Marisol Prieto Alvendaño</t>
+  </si>
+  <si>
+    <t>Martha López Patricio</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Peña Flores</t>
+  </si>
+  <si>
+    <t>Miguel González Bautista</t>
+  </si>
+  <si>
+    <t>Nelyda Hernández Palomares</t>
+  </si>
+  <si>
+    <t>Nhur Amira Núñez Ponce</t>
+  </si>
+  <si>
+    <t>Nicolás González Elizalde</t>
+  </si>
+  <si>
+    <t>Norberto Martínez Cruz</t>
+  </si>
+  <si>
+    <t>Pasiano Francisco Barranco</t>
+  </si>
+  <si>
+    <t>Ricardo Perea Gómez</t>
+  </si>
+  <si>
+    <t>Silvestre García Márquez</t>
+  </si>
+  <si>
+    <t>Sinuhe Ramírez Oviedo</t>
+  </si>
+  <si>
+    <t>Susana Rivera Cano</t>
+  </si>
+  <si>
+    <t>Tania Valdéz Cuellar</t>
+  </si>
+  <si>
+    <t>Teresa Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Ubaldo González Vargas</t>
+  </si>
+  <si>
+    <t>Vanessa Mejía Hernández</t>
+  </si>
+  <si>
+    <t>Yanet Fernández Fernández</t>
+  </si>
+  <si>
+    <t>Yaralen Cortés Mendoza</t>
+  </si>
+  <si>
+    <t>Yazmín Dávila López</t>
+  </si>
+  <si>
+    <t>Yeymi Solís Zavala</t>
+  </si>
+  <si>
+    <t>Yocelin Tovar</t>
+  </si>
+  <si>
+    <t>Zitlaly Jazmín Zúñiga</t>
+  </si>
+  <si>
+    <t>Zorayda Robles</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Mario Delgado</t>
+  </si>
+  <si>
+    <t>Rosa Icela Rodríguez</t>
+  </si>
+  <si>
+    <t>Omar García Harfuch</t>
+  </si>
+  <si>
+    <t>Marcelo Ebrard</t>
+  </si>
+  <si>
+    <t>Leticia Ramírez Amaya</t>
+  </si>
+  <si>
+    <t>Alicia Bárcena Ibarra</t>
+  </si>
+  <si>
+    <t>Josefina Rodríguez Zamora</t>
+  </si>
+  <si>
+    <t>Edna Elena Vega Rangel</t>
+  </si>
+  <si>
+    <t>Luz Elena González</t>
+  </si>
+  <si>
+    <t>Laura Itzel Castillo</t>
+  </si>
+  <si>
+    <t>Rommel Pacheco</t>
+  </si>
+  <si>
+    <t>Efraín Morales</t>
+  </si>
+  <si>
+    <t>Octavio Romero Oropeza</t>
+  </si>
+  <si>
+    <t>Martí Batres</t>
+  </si>
+  <si>
+    <t>Zoé Robledo</t>
+  </si>
+  <si>
+    <t>Alejandro Svarch</t>
+  </si>
+  <si>
+    <t>Emilia Esther Calleja</t>
+  </si>
+  <si>
+    <t>Rosaura Ruiz Gutiérrez</t>
+  </si>
+  <si>
+    <t>Raquel Buenrostro</t>
+  </si>
+  <si>
+    <t>David Kershenobich</t>
+  </si>
+  <si>
+    <t>Claudia Curiel de Icaza</t>
+  </si>
+  <si>
+    <t>María del Rocío García Pérez</t>
+  </si>
+  <si>
+    <t>Columba López Gutiérrez</t>
+  </si>
+  <si>
+    <t>Edgar Amador Zamora</t>
+  </si>
+  <si>
+    <t>Jesús Antonio Esteva Medina</t>
+  </si>
+  <si>
+    <t>Raymundo Pedro Morales Ángeles</t>
+  </si>
+  <si>
+    <t>Ricardo Trevilla Trejo</t>
+  </si>
+  <si>
+    <t>Raúl Meneses Castrejón</t>
+  </si>
+  <si>
+    <t>Tania Rodríguez Mora</t>
+  </si>
+  <si>
+    <t>Uladimir Valdez Pérezñúñez</t>
+  </si>
+  <si>
+    <t>Pablo Octavio Olvera Sánchez</t>
+  </si>
+  <si>
+    <t>Julio Valera</t>
+  </si>
+  <si>
+    <t>José Nereo Lugo Moreno</t>
+  </si>
+  <si>
+    <t>José María Alejandro Pérez</t>
+  </si>
+  <si>
+    <t>Julián Nochebuena</t>
+  </si>
+  <si>
+    <t>Hilda Miranda</t>
+  </si>
+  <si>
+    <t>Mónica Leanett Reyes</t>
+  </si>
+  <si>
+    <t>Claudia Lilia Luna</t>
+  </si>
+  <si>
+    <t>Marco Antonio Mendoza</t>
+  </si>
+  <si>
+    <t>Francisco Javier Téllez</t>
+  </si>
+  <si>
+    <t>Marlén Trejo</t>
+  </si>
+  <si>
+    <t>Orquídea Larragoiti</t>
+  </si>
+  <si>
+    <t>Johana Montcerrat Hernández</t>
+  </si>
+  <si>
+    <t>Alejandro Alcántara Carbajal</t>
+  </si>
+  <si>
+    <t>Daniel Andrade</t>
+  </si>
+  <si>
+    <t>Astrit Viridiana Cornejo</t>
+  </si>
+  <si>
+    <t>Ricardo Crespo</t>
+  </si>
+  <si>
+    <t>Alma Lidia De La Vega</t>
+  </si>
+  <si>
+    <t>Tatiana Ángeles</t>
+  </si>
+  <si>
+    <t>Mirna María de la Luz Rubio</t>
+  </si>
+  <si>
+    <t>Asael Hernández Cerón</t>
+  </si>
+  <si>
+    <t>Ciria Yamile Salomón</t>
+  </si>
+  <si>
+    <t>Javier Vázquez Calixto</t>
+  </si>
+  <si>
+    <t>Cuauhtémoc Ochoa</t>
+  </si>
+  <si>
+    <t>Carolina Viggiano</t>
+  </si>
+  <si>
+    <t>Simey Olvera</t>
+  </si>
+  <si>
+    <t>Said Vargas</t>
+  </si>
+  <si>
+    <t>Américo Villarreal</t>
+  </si>
+  <si>
+    <t>Clara Brugada</t>
+  </si>
+  <si>
+    <t>Alejandro Armenta</t>
+  </si>
+  <si>
+    <t>Delfina Gómez</t>
+  </si>
+  <si>
+    <t>Lorena Cuéllar</t>
+  </si>
+  <si>
+    <t>Tere Jiménez</t>
+  </si>
+  <si>
+    <t>Marina del Pilar Ávila</t>
+  </si>
+  <si>
+    <t>Víctor Manuel Castro</t>
+  </si>
+  <si>
+    <t>Layda Sansores</t>
+  </si>
+  <si>
+    <t>Eduardo Ramírez</t>
+  </si>
+  <si>
+    <t>María Eugenia Campos</t>
+  </si>
+  <si>
+    <t>Manolo Jiménez Salinas</t>
+  </si>
+  <si>
+    <t>Indira Vizcaíno</t>
+  </si>
+  <si>
+    <t>Esteban Villegas</t>
+  </si>
+  <si>
+    <t>Dennise García Muñoz Ledo</t>
+  </si>
+  <si>
+    <t>Evelyn Salgado</t>
+  </si>
+  <si>
+    <t>Pablo Lemus</t>
+  </si>
+  <si>
+    <t>Alfredo Ramírez Bedolla</t>
+  </si>
+  <si>
+    <t>Margarita González Saravia</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Navarro</t>
+  </si>
+  <si>
+    <t>Samuel García</t>
+  </si>
+  <si>
+    <t>Salomón Jara</t>
+  </si>
+  <si>
+    <t>Mauricio Kuri</t>
+  </si>
+  <si>
+    <t>Mara Lezama</t>
+  </si>
+  <si>
+    <t>Ricardo Gallardo</t>
+  </si>
+  <si>
+    <t>Rubén Rocha Moya</t>
+  </si>
+  <si>
+    <t>Alfonso Durazo</t>
+  </si>
+  <si>
+    <t>Javier May</t>
+  </si>
+  <si>
+    <t>Rocío Nahle</t>
+  </si>
+  <si>
+    <t>Joaquín Díaz Mena</t>
+  </si>
+  <si>
+    <t>David Monreal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -199,17 +874,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:B31" totalsRowShown="0">
-  <autoFilter ref="A1:B31"/>
-  <tableColumns count="2">
-    <tableColumn id="2" name="Diputado"/>
-    <tableColumn id="3" name="Grupo legislativo"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,266 +1138,1334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B308855-C5CC-4CF7-8DE0-6A1DCDEC6E17}">
+  <dimension ref="A1:A264"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>39</v>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>